--- a/pa-temp-fix-system.com/php/export/要改的单.xlsx
+++ b/pa-temp-fix-system.com/php/export/要改的单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17970"/>
+    <workbookView windowWidth="31770" windowHeight="17970"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,177 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>产品序号</t>
-  </si>
-  <si>
-    <t>T251105000245</t>
-  </si>
-  <si>
-    <t>T251105000246</t>
-  </si>
-  <si>
-    <t>T251105000252</t>
-  </si>
-  <si>
-    <t>T251105000253</t>
-  </si>
-  <si>
-    <t>T251105000254</t>
-  </si>
-  <si>
-    <t>T251105000255</t>
-  </si>
-  <si>
-    <t>T251105000256</t>
-  </si>
-  <si>
-    <t>T251105000257</t>
-  </si>
-  <si>
-    <t>T251105000258</t>
-  </si>
-  <si>
-    <t>T251105000270</t>
-  </si>
-  <si>
-    <t>T251105000271</t>
-  </si>
-  <si>
-    <t>T251105000272</t>
-  </si>
-  <si>
-    <t>T251105000273</t>
-  </si>
-  <si>
-    <t>T251105000275</t>
-  </si>
-  <si>
-    <t>T251105000276</t>
-  </si>
-  <si>
-    <t>T251105000284</t>
-  </si>
-  <si>
-    <t>T251105000285</t>
-  </si>
-  <si>
-    <t>T251105000287</t>
-  </si>
-  <si>
-    <t>T251105000288</t>
-  </si>
-  <si>
-    <t>T251105000289</t>
-  </si>
-  <si>
-    <t>T251105000294</t>
-  </si>
-  <si>
-    <t>T251105000304</t>
-  </si>
-  <si>
-    <t>T251105000308</t>
-  </si>
-  <si>
-    <t>T251105000309</t>
-  </si>
-  <si>
-    <t>T251105000317</t>
-  </si>
-  <si>
-    <t>T251105000318</t>
-  </si>
-  <si>
-    <t>T251105000324</t>
-  </si>
-  <si>
-    <t>T251105000325</t>
-  </si>
-  <si>
-    <t>T251105000326</t>
-  </si>
-  <si>
-    <t>T251105000328</t>
-  </si>
-  <si>
-    <t>T251105000329</t>
-  </si>
-  <si>
-    <t>T251105000330</t>
-  </si>
-  <si>
-    <t>T251105000331</t>
-  </si>
-  <si>
-    <t>T251105000332</t>
-  </si>
-  <si>
-    <t>T251105000335</t>
-  </si>
-  <si>
-    <t>T251105000336</t>
-  </si>
-  <si>
-    <t>T251105000337</t>
-  </si>
-  <si>
-    <t>T251105000338</t>
-  </si>
-  <si>
-    <t>T251105000343</t>
-  </si>
-  <si>
-    <t>T251105000344</t>
-  </si>
-  <si>
-    <t>T251105000347</t>
-  </si>
-  <si>
-    <t>T251105000348</t>
-  </si>
-  <si>
-    <t>T251105000353</t>
-  </si>
-  <si>
-    <t>T251105000354</t>
-  </si>
-  <si>
-    <t>T251105000358</t>
-  </si>
-  <si>
-    <t>T251105000359</t>
-  </si>
-  <si>
-    <t>T251105000362</t>
-  </si>
-  <si>
-    <t>T251105000366</t>
-  </si>
-  <si>
-    <t>T251105000367</t>
-  </si>
-  <si>
-    <t>T251105000378</t>
-  </si>
-  <si>
-    <t>T251105000379</t>
-  </si>
-  <si>
-    <t>T251105000385</t>
-  </si>
-  <si>
-    <t>T251105000392</t>
-  </si>
-  <si>
-    <t>T251105000393</t>
-  </si>
-  <si>
-    <t>T251105000398</t>
-  </si>
-  <si>
-    <t>T251105000399</t>
   </si>
 </sst>
 </file>
@@ -1360,7 +1192,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A57"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1371,286 +1203,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>56</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
